--- a/tinHelm/excel/DiceRule.xlsx
+++ b/tinHelm/excel/DiceRule.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17895" windowHeight="8220" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
-        <v>7001</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1">
-        <v>7002</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1">
-        <v>7003</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>14</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1">
-        <v>7004</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>16</v>
@@ -1177,12 +1177,11 @@
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1">
-        <v>7005</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>18</v>
@@ -1190,12 +1189,11 @@
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1">
-        <v>7006</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>20</v>
@@ -1203,49 +1201,36 @@
       <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D11"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14"/>
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5">
@@ -1281,7 +1266,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1">
-        <v>7001</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -1289,7 +1274,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>7002</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -1297,7 +1282,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>7003</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>14</v>
@@ -1305,7 +1290,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>7004</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>16</v>
@@ -1313,7 +1298,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>7005</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>18</v>
@@ -1321,7 +1306,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>7006</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>20</v>
